--- a/results/momentum_merged_2026-10-13.xlsx
+++ b/results/momentum_merged_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALISU</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AACI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>GFUZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,1498 +473,1326 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BCML</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>PFAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>DLHC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>SIMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>RMCF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>RSVR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>ARTW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OFLX</t>
+          <t>AUDC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>BKHAU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>BMNP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>BSET</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PWP</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQX</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CLOV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COPR</t>
+          <t>DAVE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>DMLP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>HOWL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>IBEX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GECCH</t>
+          <t>IMPP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>JANX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>KBON</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>KFFB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HYFT</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>LOPE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>MESH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KRAQ</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NNBR</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>QLEP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>QTEX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>RIGL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>SCSC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>SLSN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>POCI</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>TJGC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>ZSQR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>PENG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RWAYM</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>HEPS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BRBI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SKK</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>STDN</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>STNE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TLSA</t>
+          <t>IRIX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>LSAK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VCTR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BGM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SHLS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>ZSQR</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>RPGL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
           <t>FRSH</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SUJA</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>JDZG</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SNWV</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>GIBO</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>RZLT</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>PGNY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>KNSA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>FLYW</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MTEX</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OLB</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>HQWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
